--- a/data_lake/descensos_temperatura/dt=2026-07-24/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
+++ b/data_lake/descensos_temperatura/dt=2026-07-24/excel/PronosticoMunicipal_DescensosTemperatura_72h.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K173"/>
+  <dimension ref="A1:K224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,17 +488,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -506,17 +506,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -541,17 +541,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -559,17 +559,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>52215</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -594,17 +594,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -612,17 +612,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -647,17 +647,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -665,17 +665,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -700,17 +700,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -718,17 +718,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>52573</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Puerres</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -753,17 +753,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -771,17 +771,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -806,17 +806,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -824,17 +824,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -859,17 +859,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -877,17 +877,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -912,17 +912,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Funes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -965,17 +965,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -983,25 +983,25 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1036,17 +1036,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1071,17 +1071,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>86760</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Putumayo</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1142,17 +1142,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Tangua</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-23 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-24 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1195,17 +1195,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1248,12 +1248,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Buesaco</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>52693</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>San Sebastián</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19100</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2216,11 +2216,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Jambaló</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2269,11 +2269,11 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2308,12 +2308,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>19517</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Páez</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Corinto</t>
+          <t>Toribío</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2414,12 +2414,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Miranda</t>
+          <t>Corinto</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2428,11 +2428,11 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Miranda</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -2520,25 +2520,25 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>76275</t>
+          <t>73555</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Florida</t>
+          <t>Planadas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>76563</t>
+          <t>76275</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pradera</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2587,11 +2587,11 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>76520</t>
+          <t>76563</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Pradera</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2679,25 +2679,25 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>76248</t>
+          <t>73616</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>El Cerrito</t>
+          <t>Rioblanco</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>50370</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>Uribe</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -2785,12 +2785,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>50400</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Lejanías</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>41206</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Huila</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -2891,25 +2891,25 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>76111</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Buga</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -2944,17 +2944,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>76111</t>
+          <t>50223</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Buga</t>
+          <t>Cubarral</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -2997,17 +2997,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>25120</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3050,25 +3050,25 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>73168</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Chaparral</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3103,17 +3103,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>50318</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Guamal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3156,25 +3156,25 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>76834</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Tuluá</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3209,17 +3209,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>50006</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tuluá</t>
+          <t>Acacías</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -3262,25 +3262,25 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>50006</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Acacías</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3315,25 +3315,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>73622</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Roncesvalles</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3368,25 +3368,25 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>73622</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Roncesvalles</t>
+          <t>Arbeláez</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Gutiérrez</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3474,25 +3474,25 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>63302</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Génova</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3527,17 +3527,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>63302</t>
+          <t>73624</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Génova</t>
+          <t>Rovira</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>Fosca</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3594,11 +3594,11 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -3633,17 +3633,17 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>76736</t>
+          <t>63548</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Pijao</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Valle del Cauca</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Pasca</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3700,11 +3700,11 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3739,17 +3739,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>76736</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Valle del Cauca</t>
         </is>
       </c>
       <c r="J63" t="n">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>25754</t>
+          <t>25290</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Soacha</t>
+          <t>Fusagasugá</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>25279</t>
+          <t>25845</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Fómeque</t>
+          <t>Une</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3859,11 +3859,11 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3898,25 +3898,25 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>73001</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Ibagué</t>
+          <t>Chipaque</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -3951,17 +3951,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>63690</t>
+          <t>25740</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Salento</t>
+          <t>Sibaté</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Quindío</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>73124</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Anzoátegui</t>
+          <t>Cajamarca</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>25754</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Santa Isabel</t>
+          <t>Soacha</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>La Calera</t>
+          <t>Choachí</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>25279</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Fómeque</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4177,11 +4177,11 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -4216,17 +4216,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Junín</t>
+          <t>Ibagué</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J72" t="n">
@@ -4269,17 +4269,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>73461</t>
+          <t>63690</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Murillo</t>
+          <t>Salento</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Quindío</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -4322,17 +4322,17 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Guasca</t>
+          <t>Anzoátegui</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J74" t="n">
@@ -4375,25 +4375,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Guatavita</t>
+          <t>Santa Isabel</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4428,17 +4428,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Villamaria</t>
+          <t>La Calera</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Caldas</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J76" t="n">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>11001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Zipaquirá</t>
+          <t>Bogotá, D.C.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4495,11 +4495,11 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4534,12 +4534,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>25372</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Cogua</t>
+          <t>Junín</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tausa</t>
+          <t>Pereira</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J79" t="n">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tota</t>
+          <t>Chía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J80" t="n">
@@ -4693,25 +4693,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>73461</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Aquitania</t>
+          <t>Murillo</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4746,17 +4746,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>25322</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Monguí</t>
+          <t>Guasca</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J82" t="n">
@@ -4799,17 +4799,17 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sogamoso</t>
+          <t>Sopó</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J83" t="n">
@@ -4852,25 +4852,25 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Mongua</t>
+          <t>Santa Rosa De Cabal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Risaralda</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -4905,17 +4905,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>15820</t>
+          <t>25326</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tópaga</t>
+          <t>Guatavita</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J85" t="n">
@@ -4958,17 +4958,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Gámeza</t>
+          <t>Tocancipá</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J86" t="n">
@@ -5011,25 +5011,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Corrales</t>
+          <t>Villamaria</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5064,25 +5064,25 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>73870</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tasco</t>
+          <t>Villahermosa</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5117,17 +5117,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>25769</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Cerinza</t>
+          <t>Subachoque</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J89" t="n">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Santa Rosa De Viterbo</t>
+          <t>Sesquilé</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -5223,25 +5223,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>73152</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Duitama</t>
+          <t>Casabianca</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5276,17 +5276,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Socha</t>
+          <t>Machetá</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J92" t="n">
@@ -5329,17 +5329,17 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>15087</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Belén</t>
+          <t>Zipaquirá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J93" t="n">
@@ -5382,17 +5382,17 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>15755</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Socotá</t>
+          <t>Manizales</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Caldas</t>
         </is>
       </c>
       <c r="J94" t="n">
@@ -5435,25 +5435,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>73347</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tutazá</t>
+          <t>Herveo</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Tolima</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -5488,17 +5488,17 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>68264</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Encino</t>
+          <t>Cogua</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J96" t="n">
@@ -5541,25 +5541,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>Suesca</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5594,25 +5594,25 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>25183</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Chocontá</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5647,17 +5647,17 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Coromoro</t>
+          <t>Tausa</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J99" t="n">
@@ -5700,25 +5700,25 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>25513</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Pacho</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -5753,17 +5753,17 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>15673</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Villapinzón</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J101" t="n">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>25407</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Guacamayas</t>
+          <t>Lenguazaque</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J102" t="n">
@@ -5859,17 +5859,17 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>25653</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Panqueba</t>
+          <t>San Cayetano</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J103" t="n">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>25317</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Onzaga</t>
+          <t>Guachetá</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J104" t="n">
@@ -5965,12 +5965,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>15248</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>El Espino</t>
+          <t>Ventaquemada</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6018,25 +6018,25 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>25154</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Carmen De Carupa</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Cundinamarca</t>
         </is>
       </c>
       <c r="J106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6071,12 +6071,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>15621</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Rondón</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6085,11 +6085,11 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Chiscas</t>
+          <t>Siachoque</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6138,11 +6138,11 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6177,17 +6177,17 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>81300</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Fortul</t>
+          <t>Tota</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J109" t="n">
@@ -6230,17 +6230,17 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Guaca</t>
+          <t>Cuítiva</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J110" t="n">
@@ -6283,17 +6283,17 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>15047</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Aquitania</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J111" t="n">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>54174</t>
+          <t>15542</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Chitagá</t>
+          <t>Pesca</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J112" t="n">
@@ -6389,17 +6389,17 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Silos</t>
+          <t>Iza</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J113" t="n">
@@ -6424,17 +6424,17 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -6442,17 +6442,17 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>52560</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Potosí</t>
+          <t>Toca</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J114" t="n">
@@ -6477,17 +6477,17 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -6495,17 +6495,17 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Monguí</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J115" t="n">
@@ -6530,17 +6530,17 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -6548,17 +6548,17 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>52356</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Ipiales</t>
+          <t>Sogamoso</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J116" t="n">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>52224</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Cuaspud</t>
+          <t>Mongua</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J117" t="n">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Puerres</t>
+          <t>Tópaga</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J118" t="n">
@@ -6689,17 +6689,17 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -6707,17 +6707,17 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>52022</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Aldana</t>
+          <t>Gámeza</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J119" t="n">
@@ -6742,17 +6742,17 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -6760,17 +6760,17 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Pupiales</t>
+          <t>Corrales</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J120" t="n">
@@ -6795,17 +6795,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6813,17 +6813,17 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>52317</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Guachucal</t>
+          <t>Tasco</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J121" t="n">
@@ -6848,17 +6848,17 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>52287</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Funes</t>
+          <t>Cerinza</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J122" t="n">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -6919,25 +6919,25 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Cumbal</t>
+          <t>Santa Rosa De Viterbo</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>VERY HIGH</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -6954,17 +6954,17 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -6972,17 +6972,17 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>52720</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sapuyes</t>
+          <t>Duitama</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J124" t="n">
@@ -7007,17 +7007,17 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -7025,17 +7025,17 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>15757</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Tangua</t>
+          <t>Socha</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J125" t="n">
@@ -7060,17 +7060,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -7078,17 +7078,17 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>52838</t>
+          <t>15087</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Túquerres</t>
+          <t>Belén</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J126" t="n">
@@ -7113,17 +7113,17 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>52001</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pasto</t>
+          <t>Socotá</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J127" t="n">
@@ -7166,17 +7166,17 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -7184,17 +7184,17 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>52435</t>
+          <t>15839</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Mallama</t>
+          <t>Tutazá</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J128" t="n">
@@ -7219,17 +7219,17 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>68264</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>La Cruz</t>
+          <t>Encino</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Nariño</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J129" t="n">
@@ -7272,17 +7272,17 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -7290,17 +7290,17 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>15368</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Santa Rosa</t>
+          <t>Jericó</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J130" t="n">
@@ -7325,17 +7325,17 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -7343,17 +7343,17 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>San Sebastián</t>
+          <t>Chita</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J131" t="n">
@@ -7378,17 +7378,17 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -7396,25 +7396,25 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>19397</t>
+          <t>85136</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>La Vega</t>
+          <t>La Salina</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Casanare</t>
         </is>
       </c>
       <c r="J132" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7431,17 +7431,17 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -7449,17 +7449,17 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>41668</t>
+          <t>68217</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>San Agustín</t>
+          <t>Coromoro</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J133" t="n">
@@ -7484,17 +7484,17 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -7502,17 +7502,17 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>68167</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Saladoblanco</t>
+          <t>Charalá</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J134" t="n">
@@ -7537,17 +7537,17 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -7555,25 +7555,25 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Isnos</t>
+          <t>El Cocuy</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7590,17 +7590,17 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -7608,17 +7608,17 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>00000</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Area En Litigio Cauca - Huila</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J136" t="n">
@@ -7643,17 +7643,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -7661,17 +7661,17 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>19760</t>
+          <t>15317</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sotará</t>
+          <t>Guacamayas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J137" t="n">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -7714,17 +7714,17 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Puracé</t>
+          <t>Panqueba</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J138" t="n">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -7767,17 +7767,17 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>19824</t>
+          <t>68502</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Totoró</t>
+          <t>Onzaga</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J139" t="n">
@@ -7802,17 +7802,17 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -7820,17 +7820,17 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>15248</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Inzá</t>
+          <t>El Espino</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J140" t="n">
@@ -7855,17 +7855,17 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -7873,25 +7873,25 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Silvia</t>
+          <t>Tame</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -7908,17 +7908,17 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -7926,17 +7926,17 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>41801</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>Carcasí</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J142" t="n">
@@ -7961,17 +7961,17 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -7979,25 +7979,25 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jambaló</t>
+          <t>Güicán De La Sierra</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8014,17 +8014,17 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -8032,25 +8032,25 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>19517</t>
+          <t>15180</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Páez</t>
+          <t>Chiscas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J144" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8067,17 +8067,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -8085,17 +8085,17 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Toribío</t>
+          <t>Fortul</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Cauca</t>
+          <t>Arauca</t>
         </is>
       </c>
       <c r="J145" t="n">
@@ -8120,17 +8120,17 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -8138,17 +8138,17 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>73555</t>
+          <t>68207</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Planadas</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J146" t="n">
@@ -8173,17 +8173,17 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -8191,25 +8191,25 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>73616</t>
+          <t>68669</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Rioblanco</t>
+          <t>San Andrés</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J147" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8226,17 +8226,17 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -8244,25 +8244,25 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Uribe</t>
+          <t>Cerrito</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8279,17 +8279,17 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>50400</t>
+          <t>15223</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Lejanías</t>
+          <t>Cubará</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Boyacá</t>
         </is>
       </c>
       <c r="J149" t="n">
@@ -8332,17 +8332,17 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -8350,25 +8350,25 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>41206</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Guaca</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Huila</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J150" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8385,17 +8385,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -8403,17 +8403,17 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>68705</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Cubarral</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J151" t="n">
@@ -8438,17 +8438,17 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -8456,17 +8456,17 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>68820</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Tona</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J152" t="n">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -8509,25 +8509,25 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>73168</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Chaparral</t>
+          <t>Chitagá</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -8544,17 +8544,17 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -8562,17 +8562,17 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>50318</t>
+          <t>54743</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Guamal</t>
+          <t>Silos</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J154" t="n">
@@ -8597,17 +8597,17 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -8615,17 +8615,17 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>25649</t>
+          <t>54480</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Mutiscua</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Norte de Santander</t>
         </is>
       </c>
       <c r="J155" t="n">
@@ -8650,17 +8650,17 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-07-25 19:00</t>
+          <t>2026-07-24 19:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-07-26 07:00</t>
+          <t>2026-07-25 07:00</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -8668,17 +8668,17 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>68867</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Arbeláez</t>
+          <t>Vetas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Santander</t>
         </is>
       </c>
       <c r="J156" t="n">
@@ -8721,17 +8721,17 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>52560</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Gutiérrez</t>
+          <t>Potosí</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J157" t="n">
@@ -8774,17 +8774,17 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>52356</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Pasca</t>
+          <t>Ipiales</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J158" t="n">
@@ -8827,17 +8827,17 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>25845</t>
+          <t>52224</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Une</t>
+          <t>Cuaspud</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J159" t="n">
@@ -8880,17 +8880,17 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>52022</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Chipaque</t>
+          <t>Aldana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J160" t="n">
@@ -8933,17 +8933,17 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Bogotá, D.C.</t>
+          <t>Pupiales</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Cundinamarca</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J161" t="n">
@@ -8986,17 +8986,17 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>52317</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Chita</t>
+          <t>Guachucal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J162" t="n">
@@ -9039,25 +9039,25 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>85136</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>La Salina</t>
+          <t>Cumbal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Casanare</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J163" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>VERY HIGH</t>
         </is>
       </c>
     </row>
@@ -9092,17 +9092,17 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>52720</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>El Cocuy</t>
+          <t>Sapuyes</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J164" t="n">
@@ -9145,17 +9145,17 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>86760</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tame</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Arauca</t>
+          <t>Putumayo</t>
         </is>
       </c>
       <c r="J165" t="n">
@@ -9198,17 +9198,17 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>15332</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Güicán De La Sierra</t>
+          <t>Tangua</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Boyacá</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J166" t="n">
@@ -9251,17 +9251,17 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>52838</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Guaca</t>
+          <t>Túquerres</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J167" t="n">
@@ -9304,17 +9304,17 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>52001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Pasto</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Santander</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J168" t="n">
@@ -9357,17 +9357,17 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>54174</t>
+          <t>52435</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Chitagá</t>
+          <t>Mallama</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J169" t="n">
@@ -9410,17 +9410,17 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Silos</t>
+          <t>Buesaco</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Norte de Santander</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J170" t="n">
@@ -9463,17 +9463,17 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20001</t>
+          <t>52378</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Valledupar</t>
+          <t>La Cruz</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Nariño</t>
         </is>
       </c>
       <c r="J171" t="n">
@@ -9516,17 +9516,17 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Aracataca</t>
+          <t>Santa Rosa</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J172" t="n">
@@ -9569,23 +9569,2726 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>47001</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Santa Marta</t>
+          <t>San Sebastián</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Cauca</t>
         </is>
       </c>
       <c r="J173" t="n">
         <v>3</v>
       </c>
       <c r="K173" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>12</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>La Vega</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>12</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>41668</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>San Agustín</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>12</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Saladoblanco</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>12</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>41359</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Isnos</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>12</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>41378</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>La Argentina</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>12</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Area En Litigio Cauca - Huila</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>12</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>19760</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sotará</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>12</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>19585</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Puracé</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>12</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>73616</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Rioblanco</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-25 19:00</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-07-26 07:00</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>12</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>73168</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Chaparral</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>12</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>52560</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Potosí</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>12</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>52356</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Ipiales</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>12</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>52224</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Cuaspud</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>12</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>52573</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Puerres</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>12</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>52022</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Aldana</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>12</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>52585</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Pupiales</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>12</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>52317</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Guachucal</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>12</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>52287</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Funes</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>12</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>52227</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Cumbal</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>4</v>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>VERY HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>12</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>52720</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sapuyes</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>12</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>86760</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>12</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>52788</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Tangua</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>12</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>52838</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Túquerres</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>12</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>52001</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>12</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>52435</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Mallama</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>12</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>52110</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Buesaco</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>12</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>52699</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>12</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>19701</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Santa Rosa</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>12</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>19693</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>San Sebastián</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>12</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>La Vega</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>12</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>41668</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>San Agustín</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>12</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Saladoblanco</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>12</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>41359</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Isnos</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>12</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>41378</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>La Argentina</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>12</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>00000</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Area En Litigio Cauca - Huila</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>12</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>19760</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sotará</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>12</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>19824</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Totoró</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>12</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>19355</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Inzá</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>12</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>41801</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Teruel</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>12</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>19517</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Páez</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>12</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>19821</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Toribío</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>12</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>73555</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Planadas</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>12</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>15183</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Chita</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>12</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>85136</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>La Salina</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>12</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>15244</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>El Cocuy</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J218" t="n">
+        <v>3</v>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>12</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>15248</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>El Espino</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J219" t="n">
+        <v>3</v>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>12</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>81794</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Tame</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="J220" t="n">
+        <v>3</v>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>12</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>68152</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Carcasí</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>12</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>15332</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Güicán De La Sierra</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J222" t="n">
+        <v>3</v>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>12</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>15180</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Chiscas</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="J223" t="n">
+        <v>3</v>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>JornadaNocturna</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Nocturna</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-07-26 19:00</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-07-27 07:00</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>12</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>68207</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="J224" t="n">
+        <v>3</v>
+      </c>
+      <c r="K224" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
